--- a/mosip_master/xlsx/language.xlsx
+++ b/mosip_master/xlsx/language.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
   <si>
     <t>code</t>
   </si>
@@ -75,60 +75,6 @@
   </si>
   <si>
     <t>NULL</t>
-  </si>
-  <si>
-    <t>fra</t>
-  </si>
-  <si>
-    <t>French</t>
-  </si>
-  <si>
-    <t>français</t>
-  </si>
-  <si>
-    <t>ara</t>
-  </si>
-  <si>
-    <t>Arabic</t>
-  </si>
-  <si>
-    <t>الهندو أوروبية</t>
-  </si>
-  <si>
-    <t>kan</t>
-  </si>
-  <si>
-    <t>ಕನ್ನಡ</t>
-  </si>
-  <si>
-    <t>ಇಂಡೋ-ಯುರೋಪಿಯನ್</t>
-  </si>
-  <si>
-    <t>Kannada</t>
-  </si>
-  <si>
-    <t>hin</t>
-  </si>
-  <si>
-    <t>हिन्दी</t>
-  </si>
-  <si>
-    <t>भारोपीय</t>
-  </si>
-  <si>
-    <t>Hindi</t>
-  </si>
-  <si>
-    <t>tam</t>
-  </si>
-  <si>
-    <t>தமிழ்</t>
-  </si>
-  <si>
-    <t>இந்தோ-ஐரோப்பிய</t>
-  </si>
-  <si>
-    <t>Tamil</t>
   </si>
   <si>
     <t>es</t>
@@ -1290,8 +1236,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14.5" outlineLevelRow="7"/>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14.5" outlineLevelRow="2"/>
+  <cols>
+    <col min="3" max="3" width="17.3636363636364" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
@@ -1348,7 +1297,7 @@
         <v>14</v>
       </c>
       <c r="G2" s="1">
-        <v>45589.5135756683</v>
+        <v>45667.2623675191</v>
       </c>
       <c r="H2" t="s">
         <v>15</v>
@@ -1374,7 +1323,7 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -1383,7 +1332,7 @@
         <v>14</v>
       </c>
       <c r="G3" s="1">
-        <v>45589.5135756683</v>
+        <v>45667.2623675191</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -1395,181 +1344,6 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="1">
-        <v>45589.5135756683</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="1">
-        <v>45589.5135756683</v>
-      </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="1">
-        <v>45589.5135756683</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="1">
-        <v>45589.5135756683</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="1">
-        <v>45589.5135756683</v>
-      </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" t="s">
         <v>15</v>
       </c>
     </row>
